--- a/testCases.xlsx
+++ b/testCases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eclipseWorkspace\CucmberAutomationFramework\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eclipseWorkspace\WebAutomationFramework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3511A8-39F9-4B11-9656-0509193753CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3FF986-5E38-4849-B8FC-741422D727D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{376A7F6A-9C79-48B3-8E5A-25CB0CD90A23}"/>
   </bookViews>
@@ -711,11 +711,6 @@
   </si>
   <si>
     <t>1. Click on 'Signup/Login' option 
-2. Signin with registerd user
-3.Delete the user</t>
-  </si>
-  <si>
-    <t>1. Click on 'Signup/Login' option 
 2. Enter emailaddress and password of the deleted user and click signin</t>
   </si>
   <si>
@@ -734,9 +729,6 @@
     <t>1. The deleted user should not be logged back in</t>
   </si>
   <si>
-    <t>Validate Logging into the application using valid emal and password</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -879,6 +871,14 @@
   </si>
   <si>
     <t>1. Total price of the product is equal to quantity times the product price</t>
+  </si>
+  <si>
+    <t>Validate Logging into the application using valid email and password</t>
+  </si>
+  <si>
+    <t>1. Click on 'Signup/Login' option 
+2. Signin with registered user
+3.Delete the user</t>
   </si>
 </sst>
 </file>
@@ -1037,63 +1037,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill>
@@ -1547,7 +1491,7 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" customWidth="1"/>
     <col min="3" max="3" width="25.33203125" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" customWidth="1"/>
@@ -1584,7 +1528,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
@@ -1613,7 +1557,7 @@
         <v>17</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
@@ -1642,7 +1586,7 @@
         <v>17</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
@@ -1671,7 +1615,7 @@
         <v>17</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -1700,7 +1644,7 @@
         <v>17</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -1729,7 +1673,7 @@
         <v>17</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="165.6" x14ac:dyDescent="0.3">
@@ -1758,10 +1702,10 @@
         <v>19</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="165.6" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="207" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>110</v>
       </c>
@@ -1787,10 +1731,10 @@
         <v>19</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>111</v>
       </c>
@@ -1816,10 +1760,10 @@
         <v>23</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>112</v>
       </c>
@@ -1845,10 +1789,10 @@
         <v>23</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>113</v>
       </c>
@@ -1874,10 +1818,10 @@
         <v>23</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="138" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>114</v>
       </c>
@@ -1903,10 +1847,10 @@
         <v>23</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>115</v>
       </c>
@@ -1932,10 +1876,10 @@
         <v>23</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>116</v>
       </c>
@@ -1961,10 +1905,10 @@
         <v>23</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>117</v>
       </c>
@@ -1990,10 +1934,10 @@
         <v>23</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="138" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>118</v>
       </c>
@@ -2019,10 +1963,10 @@
         <v>23</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>119</v>
       </c>
@@ -2048,10 +1992,10 @@
         <v>23</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>120</v>
       </c>
@@ -2074,13 +2018,13 @@
         <v>49</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>121</v>
       </c>
@@ -2103,13 +2047,13 @@
         <v>51</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>103</v>
       </c>
@@ -2132,13 +2076,13 @@
         <v>53</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>122</v>
       </c>
@@ -2161,13 +2105,13 @@
         <v>56</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="69" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>123</v>
       </c>
@@ -2188,10 +2132,10 @@
         <v>89</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -2200,16 +2144,16 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="I2:I22">
-    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="NOT TESTED">
+    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="NOT TESTED">
       <formula>NOT(ISERROR(SEARCH("NOT TESTED",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="BLOCKED">
+    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="BLOCKED">
       <formula>NOT(ISERROR(SEARCH("BLOCKED",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2264,7 +2208,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
@@ -2275,7 +2219,7 @@
         <v>126</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>11</v>
@@ -2293,7 +2237,7 @@
         <v>57</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -2322,7 +2266,7 @@
         <v>60</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -2351,7 +2295,7 @@
         <v>60</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -2380,7 +2324,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -2409,7 +2353,7 @@
         <v>60</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
@@ -2438,7 +2382,7 @@
         <v>60</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -2467,7 +2411,7 @@
         <v>60</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -2496,7 +2440,7 @@
         <v>60</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
@@ -2522,10 +2466,10 @@
         <v>76</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
@@ -2551,10 +2495,10 @@
         <v>79</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
@@ -2580,10 +2524,10 @@
         <v>82</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
@@ -2609,10 +2553,10 @@
         <v>84</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="69" x14ac:dyDescent="0.3">
@@ -2641,22 +2585,22 @@
         <v>87</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="I2:I14">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="NOT TESTED">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="NOT TESTED">
       <formula>NOT(ISERROR(SEARCH("NOT TESTED",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="BLOCKED">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="BLOCKED">
       <formula>NOT(ISERROR(SEARCH("BLOCKED",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2712,13 +2656,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="55.2" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="69" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>124</v>
       </c>
@@ -2732,7 +2676,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>9</v>
@@ -2744,10 +2688,10 @@
         <v>128</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="69" x14ac:dyDescent="0.3">
@@ -2764,7 +2708,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
@@ -2776,57 +2720,57 @@
         <v>60</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2:J4">
-    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="NOT TESTED">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="NOT TESTED">
       <formula>NOT(ISERROR(SEARCH("NOT TESTED",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="BLOCKED">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="BLOCKED">
       <formula>NOT(ISERROR(SEARCH("BLOCKED",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2882,181 +2826,181 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="I5" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -3126,7 +3070,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
@@ -3134,7 +3078,7 @@
         <v>130</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>145</v>
@@ -3155,7 +3099,7 @@
         <v>144</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
@@ -3163,7 +3107,7 @@
         <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>146</v>
@@ -3184,7 +3128,7 @@
         <v>144</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
@@ -3192,10 +3136,10 @@
         <v>132</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>11</v>
@@ -3213,7 +3157,7 @@
         <v>148</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
@@ -3221,10 +3165,10 @@
         <v>133</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>11</v>
@@ -3242,7 +3186,7 @@
         <v>148</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
@@ -3250,7 +3194,7 @@
         <v>134</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>151</v>
@@ -3271,7 +3215,7 @@
         <v>150</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
@@ -3279,7 +3223,7 @@
         <v>135</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>152</v>
@@ -3300,7 +3244,7 @@
         <v>150</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="110.4" x14ac:dyDescent="0.3">
@@ -3308,10 +3252,10 @@
         <v>136</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>11</v>
@@ -3329,7 +3273,7 @@
         <v>157</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="124.2" x14ac:dyDescent="0.3">
@@ -3337,10 +3281,10 @@
         <v>137</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>11</v>
@@ -3358,7 +3302,7 @@
         <v>157</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="165.6" x14ac:dyDescent="0.3">
@@ -3366,7 +3310,7 @@
         <v>138</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>159</v>
@@ -3387,7 +3331,7 @@
         <v>161</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="151.80000000000001" x14ac:dyDescent="0.3">
@@ -3395,7 +3339,7 @@
         <v>139</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>162</v>
@@ -3410,13 +3354,13 @@
         <v>9</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="165.6" x14ac:dyDescent="0.3">
@@ -3424,7 +3368,7 @@
         <v>140</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>164</v>
@@ -3445,7 +3389,7 @@
         <v>166</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="151.80000000000001" x14ac:dyDescent="0.3">
@@ -3453,7 +3397,7 @@
         <v>141</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>167</v>
@@ -3474,7 +3418,7 @@
         <v>166</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="138" x14ac:dyDescent="0.3">
@@ -3482,7 +3426,7 @@
         <v>142</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>169</v>
@@ -3503,7 +3447,7 @@
         <v>171</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
